--- a/FEBRUARY 2026/OUTSTANDING KITCHEN/ABISEKA FEBRUARY 2026.xlsx
+++ b/FEBRUARY 2026/OUTSTANDING KITCHEN/ABISEKA FEBRUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17020"/>
+    <workbookView windowWidth="22120" windowHeight="16380"/>
   </bookViews>
   <sheets>
     <sheet name="ABISEKA (FRESH MILK)" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>DATE</t>
   </si>
@@ -62,10 +62,13 @@
     <t>FRESH MILK</t>
   </si>
   <si>
-    <t>UNPAID</t>
+    <t>PAID</t>
   </si>
   <si>
     <t>DELIVERY COST</t>
+  </si>
+  <si>
+    <t>UNPAID</t>
   </si>
 </sst>
 </file>
@@ -907,13 +910,13 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1243,6 +1246,120 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>40005</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2967355</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1711960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_5C8466ABF2E8452EB3EF4222A2E8A241" descr="PHOTO-2026-02-20-13-29-34"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9721215" y="2355215"/>
+          <a:ext cx="2927350" cy="1683385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38735</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2967355</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1759585</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_809C2067AE2540009AA232E01BA06CCC" descr="PHOTO-2026-02-22-09-57-57"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="10318750" y="3489960"/>
+          <a:ext cx="1731010" cy="2928620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>40005</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2966720</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1711960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_BBC42C6A61154005823D3BA3B3711189" descr="ABISEKA 23 FEB 2026"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9721215" y="5870575"/>
+          <a:ext cx="2926715" cy="1683385"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1606,59 +1723,101 @@
       <c r="I3" s="40"/>
       <c r="J3" s="41"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="23"/>
+    <row r="4" s="1" customFormat="1" ht="136.5" customHeight="1" spans="1:10">
+      <c r="A4" s="18">
+        <v>46073</v>
+      </c>
+      <c r="B4" s="19">
+        <v>8269</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="15">
+        <v>15</v>
+      </c>
+      <c r="E4" s="23">
+        <v>13500</v>
+      </c>
       <c r="F4" s="29"/>
       <c r="G4" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>202500</v>
       </c>
       <c r="H4" s="25">
         <f t="shared" ref="H4:H23" si="1">SUM(G4)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="23"/>
+        <v>202500</v>
+      </c>
+      <c r="I4" s="42">
+        <v>46087</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="140.3" customHeight="1" spans="1:10">
+      <c r="A5" s="18">
+        <v>46075</v>
+      </c>
+      <c r="B5" s="19">
+        <v>8303</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="15">
+        <v>15</v>
+      </c>
+      <c r="E5" s="23">
+        <v>13500</v>
+      </c>
       <c r="F5" s="29"/>
       <c r="G5" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>202500</v>
       </c>
       <c r="H5" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="23"/>
+        <v>202500</v>
+      </c>
+      <c r="I5" s="42">
+        <v>46089</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="136.55" customHeight="1" spans="1:10">
+      <c r="A6" s="18">
+        <v>46076</v>
+      </c>
+      <c r="B6" s="19">
+        <v>8325</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15">
+        <v>70</v>
+      </c>
+      <c r="E6" s="23">
+        <v>13500</v>
+      </c>
       <c r="F6" s="29"/>
       <c r="G6" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>945000</v>
       </c>
       <c r="H6" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="44"/>
+        <v>945000</v>
+      </c>
+      <c r="I6" s="42">
+        <v>46090</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
       <c r="A7" s="18"/>
@@ -1973,7 +2132,7 @@
       <c r="D24" s="22"/>
       <c r="E24" s="35">
         <f>SUM(H2:H23)-SUMIF(J:J,"PAID*",H:H)</f>
-        <v>1010000</v>
+        <v>1350000</v>
       </c>
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
@@ -1981,8 +2140,14 @@
       <c r="I24" s="35"/>
       <c r="J24" s="44"/>
     </row>
-    <row r="26" spans="7:7">
+    <row r="26" s="1" customFormat="1" spans="1:10">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
       <c r="G26" s="36"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
